--- a/storage/app/pdfs/blending_components.xlsx
+++ b/storage/app/pdfs/blending_components.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains 013 (Analisis Global)/Latinoamerica/6.  Informacion Latam/2. Blending/Entregables para herramienta/Base de datos y documentos descargables_componentes/English/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodrigofavela/Desktop/Update Blending EIH/BLENDING/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{B3F9FA0F-82D6-0242-84D8-0231938CF8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7DBC1E8-DBEB-4A4B-BFC1-85AAEC624F1B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754DDF2B-F6BA-5542-B9AE-CCA6F52F632B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5540" yWindow="980" windowWidth="23260" windowHeight="12460" tabRatio="853" firstSheet="4" activeTab="6" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
+    <workbookView xWindow="3660" yWindow="2360" windowWidth="23260" windowHeight="12460" tabRatio="853" activeTab="10" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="7" r:id="rId1"/>
@@ -663,11 +663,11 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -1092,12 +1092,12 @@
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="38" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A6" s="37"/>
+      <c r="A6" s="38"/>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
@@ -1221,7 +1221,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -1248,22 +1248,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -2175,40 +2175,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.3364873855639132</v>
+        <v>2.1257373855639128</v>
       </c>
       <c r="C24" s="25">
-        <v>2.3364872191520702</v>
+        <v>2.1257372191520698</v>
       </c>
       <c r="D24" s="25">
-        <v>2.3364872063952751</v>
+        <v>2.1257372063952746</v>
       </c>
       <c r="E24" s="25">
-        <v>2.3364872216769577</v>
+        <v>2.1257372216769572</v>
       </c>
       <c r="F24" s="25">
-        <v>2.3364872203432721</v>
+        <v>2.1257372203432716</v>
       </c>
       <c r="G24" s="25">
-        <v>2.3364872215218115</v>
+        <v>2.1257372215218111</v>
       </c>
       <c r="I24" s="28">
-        <v>2.3364872216774724</v>
+        <v>2.1257372216774719</v>
       </c>
       <c r="J24" s="15">
-        <v>2.0778502492522453</v>
+        <v>1.8671002492522448</v>
       </c>
       <c r="K24" s="15">
-        <v>1.9339969581033174</v>
+        <v>1.723246958103317</v>
       </c>
       <c r="L24" s="15">
-        <v>1.7871068229054949</v>
+        <v>1.5763568229054945</v>
       </c>
       <c r="M24" s="15">
-        <v>1.636121178776214</v>
+        <v>1.4253711787762136</v>
       </c>
       <c r="N24" s="15">
-        <v>1.5179622574256566</v>
+        <v>1.3072122574256562</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -2268,22 +2268,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -3158,40 +3158,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.5863822580466835</v>
+        <v>2.3756322580466831</v>
       </c>
       <c r="C48" s="25">
-        <v>2.5863819763808484</v>
+        <v>2.375631976380848</v>
       </c>
       <c r="D48" s="25">
-        <v>2.5863819764456135</v>
+        <v>2.3756319764456131</v>
       </c>
       <c r="E48" s="25">
-        <v>2.586381977453335</v>
+        <v>2.3756319774533345</v>
       </c>
       <c r="F48" s="25">
-        <v>2.5863819767157477</v>
+        <v>2.3756319767157472</v>
       </c>
       <c r="G48" s="25">
-        <v>2.5863819765882696</v>
+        <v>2.3756319765882692</v>
       </c>
       <c r="I48" s="28">
-        <v>2.5863824280950225</v>
+        <v>2.3756324280950221</v>
       </c>
       <c r="J48" s="15">
-        <v>2.2833471799423894</v>
+        <v>2.072597179942389</v>
       </c>
       <c r="K48" s="15">
-        <v>2.1491258652930987</v>
+        <v>1.9383758652930982</v>
       </c>
       <c r="L48" s="15">
-        <v>2.0070234527806878</v>
+        <v>1.7962734527806874</v>
       </c>
       <c r="M48" s="15">
-        <v>1.8573939214898947</v>
+        <v>1.6466439214898942</v>
       </c>
       <c r="N48" s="15">
-        <v>1.7086392312673189</v>
+        <v>1.4978892312673184</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -3234,6 +3234,51 @@
       <c r="N49" s="26">
         <v>94.999999273793492</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3254,7 +3299,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -3281,22 +3326,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -4208,40 +4253,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1564703902143068</v>
+        <v>1.9457203902143063</v>
       </c>
       <c r="C24" s="25">
-        <v>2.1564702958925843</v>
+        <v>1.9457202958925839</v>
       </c>
       <c r="D24" s="25">
-        <v>2.1564703849287423</v>
+        <v>1.9457203849287419</v>
       </c>
       <c r="E24" s="25">
-        <v>2.1564703892487898</v>
+        <v>1.9457203892487893</v>
       </c>
       <c r="F24" s="25">
-        <v>2.1564703899967648</v>
+        <v>1.9457203899967643</v>
       </c>
       <c r="G24" s="25">
-        <v>2.1564703901341695</v>
+        <v>1.9457203901341691</v>
       </c>
       <c r="I24" s="28">
-        <v>2.1564703902143068</v>
+        <v>1.9457203902143063</v>
       </c>
       <c r="J24" s="15">
-        <v>1.8848966661364022</v>
+        <v>1.6741466661364017</v>
       </c>
       <c r="K24" s="15">
-        <v>1.7335482421860602</v>
+        <v>1.5227982421860597</v>
       </c>
       <c r="L24" s="15">
-        <v>1.5915156842449603</v>
+        <v>1.3807656842449598</v>
       </c>
       <c r="M24" s="15">
-        <v>1.4473139746595611</v>
+        <v>1.2365639746595607</v>
       </c>
       <c r="N24" s="15">
-        <v>1.4767513364958667</v>
+        <v>1.2660013364958662</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -4301,22 +4346,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -5191,40 +5236,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.5363822580466837</v>
+        <v>2.3256322580466833</v>
       </c>
       <c r="C48" s="25">
-        <v>2.5363819763808486</v>
+        <v>2.3256319763808482</v>
       </c>
       <c r="D48" s="25">
-        <v>2.5363819764456137</v>
+        <v>2.3256319764456133</v>
       </c>
       <c r="E48" s="25">
-        <v>2.5363819774533352</v>
+        <v>2.3256319774533347</v>
       </c>
       <c r="F48" s="25">
-        <v>2.5363819767157478</v>
+        <v>2.3256319767157474</v>
       </c>
       <c r="G48" s="25">
-        <v>2.5363819765882698</v>
+        <v>2.3256319765882694</v>
       </c>
       <c r="I48" s="28">
-        <v>2.5363824280950227</v>
+        <v>2.3256324280950222</v>
       </c>
       <c r="J48" s="15">
-        <v>2.2333471799423896</v>
+        <v>2.0225971799423892</v>
       </c>
       <c r="K48" s="15">
-        <v>2.0991258652930989</v>
+        <v>1.8883758652930984</v>
       </c>
       <c r="L48" s="15">
-        <v>1.9570234527806878</v>
+        <v>1.7462734527806874</v>
       </c>
       <c r="M48" s="15">
-        <v>1.8073939214898946</v>
+        <v>1.5966439214898942</v>
       </c>
       <c r="N48" s="15">
-        <v>1.6586392312673188</v>
+        <v>1.4478892312673184</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -5267,6 +5312,51 @@
       <c r="N49" s="26">
         <v>94.999999273793492</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5314,22 +5404,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -6241,40 +6331,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.5124299545758504</v>
+        <v>2.30167995457585</v>
       </c>
       <c r="C24" s="25">
-        <v>2.5124299553614593</v>
+        <v>2.3016799553614589</v>
       </c>
       <c r="D24" s="25">
-        <v>2.5124299452945733</v>
+        <v>2.3016799452945729</v>
       </c>
       <c r="E24" s="25">
-        <v>2.5124299570772903</v>
+        <v>2.3016799570772899</v>
       </c>
       <c r="F24" s="25">
-        <v>2.5124299385498738</v>
+        <v>2.3016799385498734</v>
       </c>
       <c r="G24" s="25">
-        <v>2.5124299467807312</v>
+        <v>2.3016799467807307</v>
       </c>
       <c r="I24" s="28">
-        <v>2.5124299685885032</v>
+        <v>2.3016799685885028</v>
       </c>
       <c r="J24" s="15">
-        <v>2.3138083965408622</v>
+        <v>2.1030583965408618</v>
       </c>
       <c r="K24" s="15">
-        <v>2.2144977412362059</v>
+        <v>2.0037477412362055</v>
       </c>
       <c r="L24" s="15">
-        <v>2.115186865647491</v>
+        <v>1.9044368656474906</v>
       </c>
       <c r="M24" s="15">
-        <v>2.0160675398801793</v>
+        <v>1.8053175398801788</v>
       </c>
       <c r="N24" s="15">
-        <v>1.9169814193274544</v>
+        <v>1.7062314193274539</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -6334,22 +6424,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -7224,40 +7314,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.6704167466169775</v>
+        <v>2.459666746616977</v>
       </c>
       <c r="C48" s="25">
-        <v>2.6704167470675073</v>
+        <v>2.4596667470675069</v>
       </c>
       <c r="D48" s="25">
-        <v>2.6704167413293636</v>
+        <v>2.4596667413293631</v>
       </c>
       <c r="E48" s="25">
-        <v>2.6704167488260286</v>
+        <v>2.4596667488260282</v>
       </c>
       <c r="F48" s="25">
-        <v>2.6704167374881491</v>
+        <v>2.4596667374881487</v>
       </c>
       <c r="G48" s="25">
-        <v>2.6704167411862443</v>
+        <v>2.4596667411862438</v>
       </c>
       <c r="I48" s="28">
-        <v>2.670416746616977</v>
+        <v>2.4596667466169766</v>
       </c>
       <c r="J48" s="15">
-        <v>2.471795217904424</v>
+        <v>2.2610452179044236</v>
       </c>
       <c r="K48" s="15">
-        <v>2.3724844696234784</v>
+        <v>2.1617344696234779</v>
       </c>
       <c r="L48" s="15">
-        <v>2.2731748924383619</v>
+        <v>2.0624248924383615</v>
       </c>
       <c r="M48" s="15">
-        <v>2.1738629126768525</v>
+        <v>1.9631129126768521</v>
       </c>
       <c r="N48" s="15">
-        <v>2.0745521865175185</v>
+        <v>1.8638021865175181</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -7320,7 +7410,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W97"/>
+  <dimension ref="A1:W103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -7347,22 +7437,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -8274,40 +8364,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.2307458642470159</v>
+        <v>2.0199958642470155</v>
       </c>
       <c r="C24" s="25">
-        <v>2.2307458642471989</v>
+        <v>2.0199958642471985</v>
       </c>
       <c r="D24" s="25">
-        <v>2.2307458642470293</v>
+        <v>2.0199958642470288</v>
       </c>
       <c r="E24" s="25">
-        <v>2.2307458642470372</v>
+        <v>2.0199958642470368</v>
       </c>
       <c r="F24" s="25">
-        <v>2.2307458642470381</v>
+        <v>2.0199958642470377</v>
       </c>
       <c r="G24" s="25">
-        <v>2.2307458642470395</v>
+        <v>2.019995864247039</v>
       </c>
       <c r="I24" s="28">
-        <v>2.2451604546828761</v>
+        <v>2.0344104546828756</v>
       </c>
       <c r="J24" s="15">
-        <v>2.2864450155437699</v>
+        <v>2.0756950155437695</v>
       </c>
       <c r="K24" s="15">
-        <v>2.2104782058561696</v>
+        <v>1.9997282058561692</v>
       </c>
       <c r="L24" s="15">
-        <v>2.13802298056636</v>
+        <v>1.9272729805663595</v>
       </c>
       <c r="M24" s="15">
-        <v>2.067017692255424</v>
+        <v>1.8562676922554235</v>
       </c>
       <c r="N24" s="15">
-        <v>2.0048479400959409</v>
+        <v>1.7940979400959405</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -8367,22 +8457,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -9257,40 +9347,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.4226621628123697</v>
+        <v>2.2119121628123692</v>
       </c>
       <c r="C48" s="25">
-        <v>2.4226621628124807</v>
+        <v>2.2119121628124803</v>
       </c>
       <c r="D48" s="25">
-        <v>2.4226621628123723</v>
+        <v>2.2119121628123719</v>
       </c>
       <c r="E48" s="25">
-        <v>2.4226621628124279</v>
+        <v>2.2119121628124274</v>
       </c>
       <c r="F48" s="25">
-        <v>2.4226621628123572</v>
+        <v>2.2119121628123568</v>
       </c>
       <c r="G48" s="25">
-        <v>2.4226621628123577</v>
+        <v>2.2119121628123573</v>
       </c>
       <c r="I48" s="28">
-        <v>2.4226622632901429</v>
+        <v>2.2119122632901425</v>
       </c>
       <c r="J48" s="15">
-        <v>2.3952519174892748</v>
+        <v>2.1845019174892744</v>
       </c>
       <c r="K48" s="15">
-        <v>2.3309952833304286</v>
+        <v>2.1202452833304282</v>
       </c>
       <c r="L48" s="15">
-        <v>2.266262485941211</v>
+        <v>2.0555124859412106</v>
       </c>
       <c r="M48" s="15">
-        <v>2.2007731488786155</v>
+        <v>1.9900231488786151</v>
       </c>
       <c r="N48" s="15">
-        <v>2.1342464219819672</v>
+        <v>1.9234964219819668</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.15">
@@ -9336,22 +9426,22 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A52" s="12"/>
-      <c r="B52" s="38" t="s">
+      <c r="B52" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="I52" s="38" t="s">
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37"/>
+      <c r="I52" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J52" s="38"/>
-      <c r="K52" s="38"/>
-      <c r="L52" s="38"/>
-      <c r="M52" s="38"/>
-      <c r="N52" s="38"/>
+      <c r="J52" s="37"/>
+      <c r="K52" s="37"/>
+      <c r="L52" s="37"/>
+      <c r="M52" s="37"/>
+      <c r="N52" s="37"/>
     </row>
     <row r="53" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A53" s="13" t="s">
@@ -10263,40 +10353,40 @@
         <v>47</v>
       </c>
       <c r="B72" s="15">
-        <v>2.2803665559737016</v>
+        <v>2.0696165559737012</v>
       </c>
       <c r="C72" s="25">
-        <v>2.2803665557978192</v>
+        <v>2.0696165557978188</v>
       </c>
       <c r="D72" s="25">
-        <v>2.2803665559737016</v>
+        <v>2.0696165559737012</v>
       </c>
       <c r="E72" s="25">
-        <v>2.2803665559737021</v>
+        <v>2.0696165559737016</v>
       </c>
       <c r="F72" s="25">
-        <v>2.2803665559737016</v>
+        <v>2.0696165559737012</v>
       </c>
       <c r="G72" s="25">
-        <v>2.2803665559737016</v>
+        <v>2.0696165559737012</v>
       </c>
       <c r="I72" s="28">
-        <v>2.2803695742758374</v>
+        <v>2.069619574275837</v>
       </c>
       <c r="J72" s="15">
-        <v>2.2649696120573402</v>
+        <v>2.0542196120573397</v>
       </c>
       <c r="K72" s="15">
-        <v>2.1993984831578826</v>
+        <v>1.9886484831578821</v>
       </c>
       <c r="L72" s="15">
-        <v>2.1310106027618012</v>
+        <v>1.9202606027618008</v>
       </c>
       <c r="M72" s="15">
-        <v>2.0609849805505696</v>
+        <v>1.8502349805505691</v>
       </c>
       <c r="N72" s="15">
-        <v>1.9899867905323558</v>
+        <v>1.7792367905323554</v>
       </c>
       <c r="Q72" s="29"/>
       <c r="R72" s="18"/>
@@ -10356,22 +10446,22 @@
     </row>
     <row r="76" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="12"/>
-      <c r="B76" s="38" t="s">
+      <c r="B76" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C76" s="38"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="38"/>
-      <c r="I76" s="38" t="s">
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37"/>
+      <c r="I76" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J76" s="38"/>
-      <c r="K76" s="38"/>
-      <c r="L76" s="38"/>
-      <c r="M76" s="38"/>
-      <c r="N76" s="38"/>
+      <c r="J76" s="37"/>
+      <c r="K76" s="37"/>
+      <c r="L76" s="37"/>
+      <c r="M76" s="37"/>
+      <c r="N76" s="37"/>
     </row>
     <row r="77" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A77" s="13" t="s">
@@ -11246,40 +11336,40 @@
         <v>47</v>
       </c>
       <c r="B96" s="15">
-        <v>2.4749742564202921</v>
+        <v>2.2642242564202917</v>
       </c>
       <c r="C96" s="25">
-        <v>2.4749742564081894</v>
+        <v>2.2642242564081889</v>
       </c>
       <c r="D96" s="25">
-        <v>2.4749742563910386</v>
+        <v>2.2642242563910382</v>
       </c>
       <c r="E96" s="25">
-        <v>2.4749742563751016</v>
+        <v>2.2642242563751012</v>
       </c>
       <c r="F96" s="25">
-        <v>2.4749742553682954</v>
+        <v>2.264224255368295</v>
       </c>
       <c r="G96" s="25">
-        <v>2.4749742564216777</v>
+        <v>2.2642242564216772</v>
       </c>
       <c r="I96" s="28">
-        <v>2.47808376825654</v>
+        <v>2.2673337682565395</v>
       </c>
       <c r="J96" s="15">
-        <v>2.4423329945104095</v>
+        <v>2.2315829945104091</v>
       </c>
       <c r="K96" s="15">
-        <v>2.377461057682511</v>
+        <v>2.1667110576825106</v>
       </c>
       <c r="L96" s="15">
-        <v>2.3098392335962279</v>
+        <v>2.0990892335962275</v>
       </c>
       <c r="M96" s="15">
-        <v>2.2415713741675116</v>
+        <v>2.0308213741675112</v>
       </c>
       <c r="N96" s="15">
-        <v>2.1723125964182617</v>
+        <v>1.9615625964182613</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.15">
@@ -11322,6 +11412,81 @@
       <c r="N97" s="26">
         <v>91.000000000218023</v>
       </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="M99" s="8"/>
+      <c r="N99" s="8"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
+      <c r="N100" s="8"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+      <c r="M101" s="8"/>
+      <c r="N101" s="8"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+      <c r="M102" s="8"/>
+      <c r="N102" s="8"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="8"/>
+      <c r="J103" s="8"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+      <c r="M103" s="8"/>
+      <c r="N103" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -11375,22 +11540,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -12302,40 +12467,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1564703902143068</v>
+        <v>1.9457203902143063</v>
       </c>
       <c r="C24" s="25">
-        <v>2.1564702958925843</v>
+        <v>1.9457202958925839</v>
       </c>
       <c r="D24" s="25">
-        <v>2.1564703849287423</v>
+        <v>1.9457203849287419</v>
       </c>
       <c r="E24" s="25">
-        <v>2.1564703892487898</v>
+        <v>1.9457203892487893</v>
       </c>
       <c r="F24" s="25">
-        <v>2.1564703899967648</v>
+        <v>1.9457203899967643</v>
       </c>
       <c r="G24" s="25">
-        <v>2.1564703901341695</v>
+        <v>1.9457203901341691</v>
       </c>
       <c r="I24" s="28">
-        <v>2.1564703902143068</v>
+        <v>1.9457203902143063</v>
       </c>
       <c r="J24" s="15">
-        <v>1.8848966661364022</v>
+        <v>1.6741466661364017</v>
       </c>
       <c r="K24" s="15">
-        <v>1.7335482421860602</v>
+        <v>1.5227982421860597</v>
       </c>
       <c r="L24" s="15">
-        <v>1.5915156842449603</v>
+        <v>1.3807656842449598</v>
       </c>
       <c r="M24" s="15">
-        <v>1.4473139746595611</v>
+        <v>1.2365639746595607</v>
       </c>
       <c r="N24" s="15">
-        <v>1.4767513364958667</v>
+        <v>1.2660013364958662</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -12395,22 +12560,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -13284,41 +13449,41 @@
       <c r="A48" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="26">
-        <v>2.5363822580466837</v>
-      </c>
-      <c r="C48" s="27">
-        <v>2.5363819763808486</v>
-      </c>
-      <c r="D48" s="27">
-        <v>2.5363819764456137</v>
-      </c>
-      <c r="E48" s="27">
-        <v>2.5363819774533352</v>
-      </c>
-      <c r="F48" s="27">
-        <v>2.5363819767157478</v>
-      </c>
-      <c r="G48" s="27">
-        <v>2.5363819765882698</v>
+      <c r="B48" s="28">
+        <v>2.3256322580466833</v>
+      </c>
+      <c r="C48" s="15">
+        <v>2.3256319763808482</v>
+      </c>
+      <c r="D48" s="15">
+        <v>2.3256319764456133</v>
+      </c>
+      <c r="E48" s="15">
+        <v>2.3256319774533347</v>
+      </c>
+      <c r="F48" s="15">
+        <v>2.3256319767157474</v>
+      </c>
+      <c r="G48" s="15">
+        <v>2.3256319765882694</v>
       </c>
       <c r="I48" s="28">
-        <v>2.5363824280950227</v>
+        <v>2.3256324280950222</v>
       </c>
       <c r="J48" s="15">
-        <v>2.2333471799423896</v>
+        <v>2.0225971799423892</v>
       </c>
       <c r="K48" s="15">
-        <v>2.0991258652930989</v>
+        <v>1.8883758652930984</v>
       </c>
       <c r="L48" s="15">
-        <v>1.9570234527806878</v>
+        <v>1.7462734527806874</v>
       </c>
       <c r="M48" s="15">
-        <v>1.8073939214898946</v>
+        <v>1.5966439214898942</v>
       </c>
       <c r="N48" s="15">
-        <v>1.6586392312673188</v>
+        <v>1.4478892312673184</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -13381,7 +13546,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="27.6640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="26.33203125" style="8" bestFit="1" customWidth="1"/>
@@ -13410,22 +13575,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -14337,40 +14502,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.2864873855639134</v>
+        <v>2.075737385563913</v>
       </c>
       <c r="C24" s="25">
-        <v>2.2864872191520704</v>
+        <v>2.07573721915207</v>
       </c>
       <c r="D24" s="25">
-        <v>2.2864872063952753</v>
+        <v>2.0757372063952748</v>
       </c>
       <c r="E24" s="25">
-        <v>2.2864872216769578</v>
+        <v>2.0757372216769574</v>
       </c>
       <c r="F24" s="25">
-        <v>2.2864872203432722</v>
+        <v>2.0757372203432718</v>
       </c>
       <c r="G24" s="25">
-        <v>2.2864872215218117</v>
+        <v>2.0757372215218113</v>
       </c>
       <c r="I24" s="28">
-        <v>2.2864872216774725</v>
+        <v>2.0757372216774721</v>
       </c>
       <c r="J24" s="15">
-        <v>2.027850249252245</v>
+        <v>1.8171002492522446</v>
       </c>
       <c r="K24" s="15">
-        <v>1.8839969581033174</v>
+        <v>1.6732469581033169</v>
       </c>
       <c r="L24" s="15">
-        <v>1.7371068229054949</v>
+        <v>1.5263568229054945</v>
       </c>
       <c r="M24" s="15">
-        <v>1.5861211787762139</v>
+        <v>1.3753711787762135</v>
       </c>
       <c r="N24" s="15">
-        <v>1.4679622574256566</v>
+        <v>1.2572122574256561</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -14430,22 +14595,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -15320,40 +15485,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.5363822580466837</v>
+        <v>2.3256322580466833</v>
       </c>
       <c r="C48" s="25">
-        <v>2.5363819763808486</v>
+        <v>2.3256319763808482</v>
       </c>
       <c r="D48" s="25">
-        <v>2.5363819764456137</v>
+        <v>2.3256319764456133</v>
       </c>
       <c r="E48" s="25">
-        <v>2.5363819774533352</v>
+        <v>2.3256319774533347</v>
       </c>
       <c r="F48" s="25">
-        <v>2.5363819767157478</v>
+        <v>2.3256319767157474</v>
       </c>
       <c r="G48" s="25">
-        <v>2.5363819765882698</v>
+        <v>2.3256319765882694</v>
       </c>
       <c r="I48" s="28">
-        <v>2.5363824280950227</v>
+        <v>2.3256324280950222</v>
       </c>
       <c r="J48" s="15">
-        <v>2.2333471799423896</v>
+        <v>2.0225971799423892</v>
       </c>
       <c r="K48" s="15">
-        <v>2.0991258652930989</v>
+        <v>1.8883758652930984</v>
       </c>
       <c r="L48" s="15">
-        <v>1.9570234527806878</v>
+        <v>1.7462734527806874</v>
       </c>
       <c r="M48" s="15">
-        <v>1.8073939214898946</v>
+        <v>1.5966439214898942</v>
       </c>
       <c r="N48" s="15">
-        <v>1.6586392312673188</v>
+        <v>1.4478892312673184</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -15396,6 +15561,51 @@
       <c r="N49" s="26">
         <v>94.999999273793492</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -15416,7 +15626,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -15443,22 +15653,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -16370,40 +16580,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.4101630681585871</v>
+        <v>2.1994130681585866</v>
       </c>
       <c r="C24" s="25">
-        <v>2.4120348725002265</v>
+        <v>2.2012848725002261</v>
       </c>
       <c r="D24" s="25">
-        <v>2.4120348725002265</v>
+        <v>2.2012848725002261</v>
       </c>
       <c r="E24" s="25">
-        <v>2.4120348725009375</v>
+        <v>2.2012848725009371</v>
       </c>
       <c r="F24" s="25">
-        <v>2.4014651830015898</v>
+        <v>2.1907151830015894</v>
       </c>
       <c r="G24" s="25">
-        <v>2.4120348725002265</v>
+        <v>2.2012848725002261</v>
       </c>
       <c r="I24" s="28">
-        <v>2.4120348725002265</v>
+        <v>2.2012848725002261</v>
       </c>
       <c r="J24" s="15">
-        <v>2.241790305154669</v>
+        <v>2.0310403051546686</v>
       </c>
       <c r="K24" s="15">
-        <v>2.1554870262152028</v>
+        <v>1.9447370262152024</v>
       </c>
       <c r="L24" s="15">
-        <v>2.070256671129203</v>
+        <v>1.8595066711292025</v>
       </c>
       <c r="M24" s="15">
-        <v>1.9951403819659093</v>
+        <v>1.7843903819659088</v>
       </c>
       <c r="N24" s="15">
-        <v>1.9081855184637724</v>
+        <v>1.6974355184637719</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -16463,22 +16673,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -17353,40 +17563,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.6228177973290903</v>
+        <v>2.4120677973290898</v>
       </c>
       <c r="C48" s="25">
-        <v>2.5608714819635416</v>
+        <v>2.3501214819635412</v>
       </c>
       <c r="D48" s="25">
-        <v>2.5449528075282393</v>
+        <v>2.3342028075282388</v>
       </c>
       <c r="E48" s="25">
-        <v>2.5309077111287643</v>
+        <v>2.3201577111287639</v>
       </c>
       <c r="F48" s="25">
-        <v>2.5149207070075876</v>
+        <v>2.3041707070075872</v>
       </c>
       <c r="G48" s="25">
-        <v>2.4959377698234988</v>
+        <v>2.2851877698234984</v>
       </c>
       <c r="I48" s="28">
-        <v>2.6720767348188068</v>
+        <v>2.4613267348188064</v>
       </c>
       <c r="J48" s="15">
-        <v>2.48297269546137</v>
+        <v>2.2722226954613696</v>
       </c>
       <c r="K48" s="15">
-        <v>2.3954693499572746</v>
+        <v>2.1847193499572741</v>
       </c>
       <c r="L48" s="15">
-        <v>2.3091660365626061</v>
+        <v>2.0984160365626057</v>
       </c>
       <c r="M48" s="15">
-        <v>2.2228749759409787</v>
+        <v>2.0121249759409783</v>
       </c>
       <c r="N48" s="15">
-        <v>2.1381173073574744</v>
+        <v>1.927367307357474</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -17429,6 +17639,51 @@
       <c r="N49" s="26">
         <v>95</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -17449,7 +17704,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:W52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="30.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -17471,22 +17726,22 @@
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A3" s="12"/>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="I3" s="38" t="s">
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="I3" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
     </row>
     <row r="4" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A4" s="13" t="s">
@@ -18398,40 +18653,40 @@
         <v>47</v>
       </c>
       <c r="B23" s="15">
-        <v>2.3749594973500967</v>
+        <v>2.1642094973500963</v>
       </c>
       <c r="C23" s="25">
-        <v>2.3749594958096538</v>
+        <v>2.1642094958096534</v>
       </c>
       <c r="D23" s="25">
-        <v>2.3749597897558643</v>
+        <v>2.1642097897558639</v>
       </c>
       <c r="E23" s="25">
-        <v>2.3749594662050226</v>
+        <v>2.1642094662050222</v>
       </c>
       <c r="F23" s="25">
-        <v>2.3749594858204657</v>
+        <v>2.1642094858204652</v>
       </c>
       <c r="G23" s="25">
-        <v>2.374959486181162</v>
+        <v>2.1642094861811616</v>
       </c>
       <c r="I23" s="28">
-        <v>2.4325003332189863</v>
+        <v>2.2217503332189859</v>
       </c>
       <c r="J23" s="15">
-        <v>2.2389081290127888</v>
+        <v>2.0281581290127884</v>
       </c>
       <c r="K23" s="15">
-        <v>2.1087726069444601</v>
+        <v>1.8980226069444597</v>
       </c>
       <c r="L23" s="15">
-        <v>2.0124891649138998</v>
+        <v>1.8017391649138994</v>
       </c>
       <c r="M23" s="15">
-        <v>1.9122885194647534</v>
+        <v>1.701538519464753</v>
       </c>
       <c r="N23" s="15">
-        <v>1.8068978437419301</v>
+        <v>1.5961478437419296</v>
       </c>
       <c r="Q23" s="29"/>
       <c r="R23" s="18"/>
@@ -18491,22 +18746,22 @@
     </row>
     <row r="27" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="12"/>
-      <c r="B27" s="38" t="s">
+      <c r="B27" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="I27" s="38" t="s">
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="I27" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J27" s="38"/>
-      <c r="K27" s="38"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="37"/>
     </row>
     <row r="28" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A28" s="13" t="s">
@@ -19381,40 +19636,40 @@
         <v>47</v>
       </c>
       <c r="B47" s="15">
-        <v>2.5012040330428187</v>
+        <v>2.2904540330428182</v>
       </c>
       <c r="C47" s="25">
-        <v>2.5012040078511313</v>
+        <v>2.2904540078511308</v>
       </c>
       <c r="D47" s="25">
-        <v>2.5012043452101986</v>
+        <v>2.2904543452101982</v>
       </c>
       <c r="E47" s="25">
-        <v>2.5012040297890077</v>
+        <v>2.2904540297890073</v>
       </c>
       <c r="F47" s="25">
-        <v>2.5012040323351497</v>
+        <v>2.2904540323351492</v>
       </c>
       <c r="G47" s="25">
-        <v>2.5012040296562028</v>
+        <v>2.2904540296562024</v>
       </c>
       <c r="I47" s="28">
-        <v>2.5188702951985125</v>
+        <v>2.308120295198512</v>
       </c>
       <c r="J47" s="15">
-        <v>2.3331657353454176</v>
+        <v>2.1224157353454172</v>
       </c>
       <c r="K47" s="15">
-        <v>2.228760834298547</v>
+        <v>2.0180108342985466</v>
       </c>
       <c r="L47" s="15">
-        <v>2.1201935794084434</v>
+        <v>1.909443579408443</v>
       </c>
       <c r="M47" s="15">
-        <v>2.0079854758809423</v>
+        <v>1.7972354758809419</v>
       </c>
       <c r="N47" s="15">
-        <v>1.907152318302755</v>
+        <v>1.6964023183027546</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.15">
@@ -19457,6 +19712,51 @@
       <c r="N48" s="26">
         <v>97.499999851009946</v>
       </c>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -19508,22 +19808,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -20453,40 +20753,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.2819324342132092</v>
+        <v>2.0711824342132088</v>
       </c>
       <c r="C24" s="25">
-        <v>2.2819324342132092</v>
+        <v>2.0711824342132088</v>
       </c>
       <c r="D24" s="25">
-        <v>2.2819344010022244</v>
+        <v>2.071184401002224</v>
       </c>
       <c r="E24" s="25">
-        <v>2.2819324342132092</v>
+        <v>2.0711824342132088</v>
       </c>
       <c r="F24" s="25">
-        <v>2.2819324342132092</v>
+        <v>2.0711824342132088</v>
       </c>
       <c r="G24" s="25">
-        <v>2.2819324342132092</v>
+        <v>2.0711824342132088</v>
       </c>
       <c r="I24" s="15">
-        <v>2.2819324342132092</v>
+        <v>2.0711824342132088</v>
       </c>
       <c r="J24" s="25">
-        <v>2.0391818701169671</v>
+        <v>1.8284318701169666</v>
       </c>
       <c r="K24" s="25">
-        <v>1.9767890161952066</v>
+        <v>1.7660390161952062</v>
       </c>
       <c r="L24" s="25">
-        <v>1.9157263484108893</v>
+        <v>1.7049763484108889</v>
       </c>
       <c r="M24" s="25">
-        <v>1.8532013451852976</v>
+        <v>1.6424513451852971</v>
       </c>
       <c r="N24" s="25">
-        <v>1.7904451447271583</v>
+        <v>1.5796951447271579</v>
       </c>
       <c r="P24" s="32"/>
       <c r="Q24" s="29"/>
@@ -20548,22 +20848,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -21517,22 +21817,22 @@
     </row>
     <row r="52" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="12"/>
-      <c r="B52" s="38" t="s">
+      <c r="B52" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="I52" s="38" t="s">
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37"/>
+      <c r="I52" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J52" s="38"/>
-      <c r="K52" s="38"/>
-      <c r="L52" s="38"/>
-      <c r="M52" s="38"/>
-      <c r="N52" s="38"/>
+      <c r="J52" s="37"/>
+      <c r="K52" s="37"/>
+      <c r="L52" s="37"/>
+      <c r="M52" s="37"/>
+      <c r="N52" s="37"/>
     </row>
     <row r="53" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A53" s="13" t="s">
@@ -22444,40 +22744,40 @@
         <v>47</v>
       </c>
       <c r="B72" s="15">
-        <v>2.1318928006378051</v>
+        <v>1.9211428006378046</v>
       </c>
       <c r="C72" s="25">
-        <v>2.1318928065310443</v>
+        <v>1.9211428065310439</v>
       </c>
       <c r="D72" s="25">
-        <v>2.1318928065310443</v>
+        <v>1.9211428065310439</v>
       </c>
       <c r="E72" s="25">
-        <v>2.1318928065310438</v>
+        <v>1.9211428065310434</v>
       </c>
       <c r="F72" s="25">
-        <v>2.1318928065310443</v>
+        <v>1.9211428065310439</v>
       </c>
       <c r="G72" s="25">
-        <v>2.1318928065311029</v>
+        <v>1.9211428065311025</v>
       </c>
       <c r="I72" s="15">
-        <v>2.1325278635908629</v>
+        <v>1.9217778635908624</v>
       </c>
       <c r="J72" s="25">
-        <v>2.0090673452596794</v>
+        <v>1.798317345259679</v>
       </c>
       <c r="K72" s="25">
-        <v>1.9485650667193097</v>
+        <v>1.7378150667193093</v>
       </c>
       <c r="L72" s="25">
-        <v>1.8877684130588959</v>
+        <v>1.6770184130588954</v>
       </c>
       <c r="M72" s="25">
-        <v>1.8285334194720209</v>
+        <v>1.6177834194720204</v>
       </c>
       <c r="N72" s="25">
-        <v>1.7682471958877393</v>
+        <v>1.5574971958877388</v>
       </c>
       <c r="Q72" s="29"/>
       <c r="R72" s="18"/>
@@ -22537,22 +22837,22 @@
     </row>
     <row r="76" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="12"/>
-      <c r="B76" s="38" t="s">
+      <c r="B76" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C76" s="38"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="38"/>
-      <c r="I76" s="38" t="s">
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37"/>
+      <c r="I76" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J76" s="38"/>
-      <c r="K76" s="38"/>
-      <c r="L76" s="38"/>
-      <c r="M76" s="38"/>
-      <c r="N76" s="38"/>
+      <c r="J76" s="37"/>
+      <c r="K76" s="37"/>
+      <c r="L76" s="37"/>
+      <c r="M76" s="37"/>
+      <c r="N76" s="37"/>
     </row>
     <row r="77" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A77" s="13" t="s">
@@ -23427,40 +23727,40 @@
         <v>47</v>
       </c>
       <c r="B96" s="15">
-        <v>2.315013312667578</v>
+        <v>2.1042633126675776</v>
       </c>
       <c r="C96" s="25">
-        <v>2.3150133171490372</v>
+        <v>2.1042633171490368</v>
       </c>
       <c r="D96" s="25">
-        <v>2.3150133171490879</v>
+        <v>2.1042633171490874</v>
       </c>
       <c r="E96" s="25">
-        <v>2.3150133171490372</v>
+        <v>2.1042633171490368</v>
       </c>
       <c r="F96" s="25">
-        <v>2.3150133171490377</v>
+        <v>2.1042633171490372</v>
       </c>
       <c r="G96" s="25">
-        <v>2.3150133171490372</v>
+        <v>2.1042633171490368</v>
       </c>
       <c r="I96" s="15">
-        <v>2.316322529449665</v>
+        <v>2.1055725294496646</v>
       </c>
       <c r="J96" s="25">
-        <v>2.1921139460748895</v>
+        <v>1.9813639460748891</v>
       </c>
       <c r="K96" s="25">
-        <v>2.1318338593063939</v>
+        <v>1.9210838593063935</v>
       </c>
       <c r="L96" s="25">
-        <v>2.070874104407991</v>
+        <v>1.8601241044079906</v>
       </c>
       <c r="M96" s="25">
-        <v>2.0086316284558996</v>
+        <v>1.7978816284558992</v>
       </c>
       <c r="N96" s="25">
-        <v>1.9450765320795134</v>
+        <v>1.7343265320795129</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.15">
@@ -23527,7 +23827,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="8" customWidth="1"/>
@@ -23554,22 +23854,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -24481,40 +24781,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.2611352598671521</v>
+        <v>2.0503852598671517</v>
       </c>
       <c r="C24" s="25">
-        <v>2.2611353303958657</v>
+        <v>2.0503853303958652</v>
       </c>
       <c r="D24" s="25">
-        <v>2.2611353303975292</v>
+        <v>2.0503853303975288</v>
       </c>
       <c r="E24" s="25">
-        <v>2.2611353303981163</v>
+        <v>2.0503853303981159</v>
       </c>
       <c r="F24" s="25">
-        <v>2.2611353303954389</v>
+        <v>2.0503853303954385</v>
       </c>
       <c r="G24" s="25">
-        <v>2.2611353303985462</v>
+        <v>2.0503853303985458</v>
       </c>
       <c r="I24" s="28">
-        <v>2.2611353303990014</v>
+        <v>2.0503853303990009</v>
       </c>
       <c r="J24" s="15">
-        <v>1.955909340255984</v>
+        <v>1.7451593402559835</v>
       </c>
       <c r="K24" s="15">
-        <v>1.793362191448171</v>
+        <v>1.5826121914481706</v>
       </c>
       <c r="L24" s="15">
-        <v>1.6222770830527296</v>
+        <v>1.4115270830527291</v>
       </c>
       <c r="M24" s="15">
-        <v>1.4421168257215398</v>
+        <v>1.2313668257215393</v>
       </c>
       <c r="N24" s="15">
-        <v>1.5431385972100584</v>
+        <v>1.332388597210058</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -24574,22 +24874,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -25464,40 +25764,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.7645701813215036</v>
+        <v>2.5538201813215031</v>
       </c>
       <c r="C48" s="25">
-        <v>2.7645701813215036</v>
+        <v>2.5538201813215031</v>
       </c>
       <c r="D48" s="25">
-        <v>2.7645701813215036</v>
+        <v>2.5538201813215031</v>
       </c>
       <c r="E48" s="25">
-        <v>2.7645701813215031</v>
+        <v>2.5538201813215027</v>
       </c>
       <c r="F48" s="25">
-        <v>2.7645701811831644</v>
+        <v>2.553820181183164</v>
       </c>
       <c r="G48" s="25">
-        <v>2.76457018085839</v>
+        <v>2.5538201808583896</v>
       </c>
       <c r="I48" s="28">
-        <v>2.764570188023066</v>
+        <v>2.5538201880230655</v>
       </c>
       <c r="J48" s="15">
-        <v>2.5046953475676794</v>
+        <v>2.293945347567679</v>
       </c>
       <c r="K48" s="15">
-        <v>2.3678707793690248</v>
+        <v>2.1571207793690244</v>
       </c>
       <c r="L48" s="15">
-        <v>2.2248900669148126</v>
+        <v>2.0141400669148122</v>
       </c>
       <c r="M48" s="15">
-        <v>2.0746903576571709</v>
+        <v>1.8639403576571705</v>
       </c>
       <c r="N48" s="15">
-        <v>1.9162316261970185</v>
+        <v>1.705481626197018</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -25540,6 +25840,51 @@
       <c r="N49" s="26">
         <v>94.999999999250733</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -25561,7 +25906,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="26.33203125" style="8" bestFit="1" customWidth="1"/>
@@ -25590,22 +25935,22 @@
     </row>
     <row r="4" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:14" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -26012,40 +26357,40 @@
         <v>47</v>
       </c>
       <c r="B16" s="33">
-        <v>2.4017316744158363</v>
+        <v>2.1909816744158359</v>
       </c>
       <c r="C16" s="34">
-        <v>2.4017316744158586</v>
+        <v>2.1909816744158581</v>
       </c>
       <c r="D16" s="34">
-        <v>2.4017316744158204</v>
+        <v>2.1909816744158199</v>
       </c>
       <c r="E16" s="34">
-        <v>2.4017316744157</v>
+        <v>2.1909816744156996</v>
       </c>
       <c r="F16" s="34">
-        <v>2.4017316743918542</v>
+        <v>2.1909816743918538</v>
       </c>
       <c r="G16" s="34">
-        <v>2.4017316744159483</v>
+        <v>2.1909816744159478</v>
       </c>
       <c r="I16" s="34">
-        <v>2.6010714817233795</v>
+        <v>2.3903214817233791</v>
       </c>
       <c r="J16" s="35">
-        <v>2.5191281483900463</v>
+        <v>2.3083781483900458</v>
       </c>
       <c r="K16" s="35">
-        <v>2.4297928773843864</v>
+        <v>2.219042877384386</v>
       </c>
       <c r="L16" s="35">
-        <v>2.3413716054914016</v>
+        <v>2.1306216054914011</v>
       </c>
       <c r="M16" s="35">
-        <v>2.2492940489851354</v>
+        <v>2.038544048985135</v>
       </c>
       <c r="N16" s="35">
-        <v>2.1602170102978442</v>
+        <v>1.9494670102978437</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.15">
@@ -26094,22 +26439,22 @@
     </row>
     <row r="19" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="12"/>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="I19" s="38" t="s">
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="I19" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="37"/>
+      <c r="N19" s="37"/>
     </row>
     <row r="20" spans="1:14" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="13" t="s">
@@ -26516,40 +26861,40 @@
         <v>47</v>
       </c>
       <c r="B31" s="33">
-        <v>2.7300992058067082</v>
+        <v>2.5193492058067077</v>
       </c>
       <c r="C31" s="34">
-        <v>2.7301015539625801</v>
+        <v>2.5193515539625797</v>
       </c>
       <c r="D31" s="34">
-        <v>2.7300992058067362</v>
+        <v>2.5193492058067357</v>
       </c>
       <c r="E31" s="34">
-        <v>2.7300992058002849</v>
+        <v>2.5193492058002844</v>
       </c>
       <c r="F31" s="34">
-        <v>2.7300992058053124</v>
+        <v>2.519349205805312</v>
       </c>
       <c r="G31" s="34">
-        <v>2.7300992059804781</v>
+        <v>2.5193492059804776</v>
       </c>
       <c r="I31" s="34">
-        <v>2.7268264017597152</v>
+        <v>2.5160764017597148</v>
       </c>
       <c r="J31" s="35">
-        <v>2.6448830684263815</v>
+        <v>2.4341330684263811</v>
       </c>
       <c r="K31" s="35">
-        <v>2.5665562950998329</v>
+        <v>2.3558062950998324</v>
       </c>
       <c r="L31" s="35">
-        <v>2.4868883189622575</v>
+        <v>2.276138318962257</v>
       </c>
       <c r="M31" s="35">
-        <v>2.1327840216481424</v>
+        <v>1.922034021648142</v>
       </c>
       <c r="N31" s="35">
-        <v>2.077259477536098</v>
+        <v>1.8665094775360975</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.15">
@@ -26598,22 +26943,22 @@
     </row>
     <row r="34" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="12"/>
-      <c r="B34" s="38" t="s">
+      <c r="B34" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="I34" s="38" t="s">
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="I34" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J34" s="38"/>
-      <c r="K34" s="38"/>
-      <c r="L34" s="38"/>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37"/>
     </row>
     <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="13" t="s">
@@ -27020,40 +27365,40 @@
         <v>47</v>
       </c>
       <c r="B46" s="33">
-        <v>2.6011911170968061</v>
+        <v>2.3904411170968056</v>
       </c>
       <c r="C46" s="34">
-        <v>2.6011933363445894</v>
+        <v>2.3904433363445889</v>
       </c>
       <c r="D46" s="34">
-        <v>2.6011911170843316</v>
+        <v>2.3904411170843312</v>
       </c>
       <c r="E46" s="34">
-        <v>2.6011887264629663</v>
+        <v>2.3904387264629658</v>
       </c>
       <c r="F46" s="34">
-        <v>2.6011911170164552</v>
+        <v>2.3904411170164548</v>
       </c>
       <c r="G46" s="34">
-        <v>2.6011911176649467</v>
+        <v>2.3904411176649463</v>
       </c>
       <c r="I46" s="15">
-        <v>2.6010714817232987</v>
+        <v>2.3903214817232983</v>
       </c>
       <c r="J46" s="25">
-        <v>2.5191281483899655</v>
+        <v>2.308378148389965</v>
       </c>
       <c r="K46" s="25">
-        <v>2.4297928461200278</v>
+        <v>2.2190428461200273</v>
       </c>
       <c r="L46" s="25">
-        <v>2.3413715539396418</v>
+        <v>2.1306215539396414</v>
       </c>
       <c r="M46" s="25">
-        <v>2.2492892558901905</v>
+        <v>2.03853925589019</v>
       </c>
       <c r="N46" s="25">
-        <v>2.1602226224295684</v>
+        <v>1.949472622429568</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.15">
@@ -27102,22 +27447,22 @@
     </row>
     <row r="49" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="12"/>
-      <c r="B49" s="38" t="s">
+      <c r="B49" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="I49" s="38" t="s">
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37"/>
+      <c r="I49" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J49" s="38"/>
-      <c r="K49" s="38"/>
-      <c r="L49" s="38"/>
-      <c r="M49" s="38"/>
-      <c r="N49" s="38"/>
+      <c r="J49" s="37"/>
+      <c r="K49" s="37"/>
+      <c r="L49" s="37"/>
+      <c r="M49" s="37"/>
+      <c r="N49" s="37"/>
     </row>
     <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="13" t="s">
@@ -27524,40 +27869,40 @@
         <v>47</v>
       </c>
       <c r="B61" s="33">
-        <v>2.7300992058067082</v>
+        <v>2.5193492058067077</v>
       </c>
       <c r="C61" s="34">
-        <v>2.7301015539625806</v>
+        <v>2.5193515539625801</v>
       </c>
       <c r="D61" s="34">
-        <v>2.7300992085602553</v>
+        <v>2.5193492085602549</v>
       </c>
       <c r="E61" s="34">
-        <v>2.7300992050420172</v>
+        <v>2.5193492050420168</v>
       </c>
       <c r="F61" s="34">
-        <v>2.73009668560807</v>
+        <v>2.5193466856080695</v>
       </c>
       <c r="G61" s="34">
-        <v>2.7300992058067193</v>
+        <v>2.5193492058067188</v>
       </c>
       <c r="I61" s="15">
-        <v>2.7106061419544782</v>
+        <v>2.4998561419544778</v>
       </c>
       <c r="J61" s="25">
-        <v>2.6286628086211445</v>
+        <v>2.4179128086211441</v>
       </c>
       <c r="K61" s="25">
-        <v>2.5498170352159613</v>
+        <v>2.3390670352159608</v>
       </c>
       <c r="L61" s="25">
-        <v>2.4700559056936142</v>
+        <v>2.2593059056936138</v>
       </c>
       <c r="M61" s="25">
-        <v>2.3874345031613915</v>
+        <v>2.1766845031613911</v>
       </c>
       <c r="N61" s="25">
-        <v>2.3207717940373196</v>
+        <v>2.1100217940373192</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.15">
@@ -27606,22 +27951,22 @@
     </row>
     <row r="64" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="12"/>
-      <c r="B64" s="38" t="s">
+      <c r="B64" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="I64" s="38" t="s">
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="37"/>
+      <c r="I64" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J64" s="38"/>
-      <c r="K64" s="38"/>
-      <c r="L64" s="38"/>
-      <c r="M64" s="38"/>
-      <c r="N64" s="38"/>
+      <c r="J64" s="37"/>
+      <c r="K64" s="37"/>
+      <c r="L64" s="37"/>
+      <c r="M64" s="37"/>
+      <c r="N64" s="37"/>
     </row>
     <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="13" t="s">
@@ -27976,40 +28321,40 @@
         <v>47</v>
       </c>
       <c r="B76" s="33">
-        <v>2.3307861577255169</v>
+        <v>2.1200361577255165</v>
       </c>
       <c r="C76" s="34">
-        <v>2.3307881065683409</v>
+        <v>2.1200381065683405</v>
       </c>
       <c r="D76" s="34">
-        <v>2.3307861577254854</v>
+        <v>2.1200361577254849</v>
       </c>
       <c r="E76" s="34">
-        <v>2.3307861577253721</v>
+        <v>2.1200361577253717</v>
       </c>
       <c r="F76" s="34">
-        <v>2.3307840706563967</v>
+        <v>2.1200340706563963</v>
       </c>
       <c r="G76" s="34">
-        <v>2.3307861576973057</v>
+        <v>2.1200361576973052</v>
       </c>
       <c r="I76" s="15">
-        <v>2.4643243321203681</v>
+        <v>2.2535743321203676</v>
       </c>
       <c r="J76" s="25">
-        <v>2.3823810316418976</v>
+        <v>2.1716310316418972</v>
       </c>
       <c r="K76" s="25">
-        <v>2.297753846387578</v>
+        <v>2.0870038463875775</v>
       </c>
       <c r="L76" s="25">
-        <v>2.2104456425148338</v>
+        <v>1.9996956425148333</v>
       </c>
       <c r="M76" s="25">
-        <v>2.1360432879082181</v>
+        <v>1.9252932879082176</v>
       </c>
       <c r="N76" s="25">
-        <v>2.0548936256457822</v>
+        <v>1.8441436256457817</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.15">
@@ -28058,22 +28403,22 @@
     </row>
     <row r="79" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="12"/>
-      <c r="B79" s="38" t="s">
+      <c r="B79" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="I79" s="38" t="s">
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="37"/>
+      <c r="F79" s="37"/>
+      <c r="G79" s="37"/>
+      <c r="I79" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J79" s="38"/>
-      <c r="K79" s="38"/>
-      <c r="L79" s="38"/>
-      <c r="M79" s="38"/>
-      <c r="N79" s="38"/>
+      <c r="J79" s="37"/>
+      <c r="K79" s="37"/>
+      <c r="L79" s="37"/>
+      <c r="M79" s="37"/>
+      <c r="N79" s="37"/>
     </row>
     <row r="80" spans="1:14" ht="15" x14ac:dyDescent="0.15">
       <c r="A80" s="13" t="s">
@@ -28428,40 +28773,40 @@
         <v>47</v>
       </c>
       <c r="B91" s="33">
-        <v>2.5577944696002204</v>
+        <v>2.34704446960022</v>
       </c>
       <c r="C91" s="34">
-        <v>2.5577966454513561</v>
+        <v>2.3470466454513557</v>
       </c>
       <c r="D91" s="34">
-        <v>2.557792121391075</v>
+        <v>2.3470421213910746</v>
       </c>
       <c r="E91" s="34">
-        <v>2.5577944696002106</v>
+        <v>2.3470444696002102</v>
       </c>
       <c r="F91" s="34">
-        <v>2.5577921213932515</v>
+        <v>2.3470421213932511</v>
       </c>
       <c r="G91" s="34">
-        <v>2.5577932571798714</v>
+        <v>2.3470432571798709</v>
       </c>
       <c r="I91" s="15">
-        <v>2.555194766327467</v>
+        <v>2.3444447663274666</v>
       </c>
       <c r="J91" s="25">
-        <v>2.4732514658489966</v>
+        <v>2.2625014658489961</v>
       </c>
       <c r="K91" s="25">
-        <v>2.3879396141602993</v>
+        <v>2.1771896141602989</v>
       </c>
       <c r="L91" s="25">
-        <v>2.31123954942308</v>
+        <v>2.1004895494230795</v>
       </c>
       <c r="M91" s="25">
-        <v>2.2349255104229333</v>
+        <v>2.0241755104229329</v>
       </c>
       <c r="N91" s="25">
-        <v>2.1659182024026276</v>
+        <v>1.9551682024026271</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.15">
@@ -28504,6 +28849,111 @@
       <c r="N92" s="27">
         <v>96.999999999997868</v>
       </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+      <c r="M94" s="8"/>
+      <c r="N94" s="8"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+      <c r="M95" s="8"/>
+      <c r="N95" s="8"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+      <c r="M96" s="8"/>
+      <c r="N96" s="8"/>
+    </row>
+    <row r="97" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="8"/>
+      <c r="N97" s="8"/>
+    </row>
+    <row r="98" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="8"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+      <c r="M98" s="8"/>
+      <c r="N98" s="8"/>
+    </row>
+    <row r="99" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="M99" s="8"/>
+      <c r="N99" s="8"/>
+    </row>
+    <row r="100" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
+      <c r="N100" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -28532,7 +28982,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -28559,22 +29009,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -29438,40 +29888,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.3279700003396275</v>
+        <v>2.1172200003396271</v>
       </c>
       <c r="C24" s="25">
-        <v>2.3281931914625087</v>
+        <v>2.1174431914625083</v>
       </c>
       <c r="D24" s="25">
-        <v>2.3285975639680281</v>
+        <v>2.1178475639680276</v>
       </c>
       <c r="E24" s="25">
-        <v>2.3291009099009194</v>
+        <v>2.118350909900919</v>
       </c>
       <c r="F24" s="25">
-        <v>2.3289097997974109</v>
+        <v>2.1181597997974104</v>
       </c>
       <c r="G24" s="25">
-        <v>2.3300544401498673</v>
+        <v>2.1193044401498669</v>
       </c>
       <c r="I24" s="28">
-        <v>2.259820264519929</v>
+        <v>2.0490702645199286</v>
       </c>
       <c r="J24" s="15">
-        <v>2.1328616666299549</v>
+        <v>1.9221116666299545</v>
       </c>
       <c r="K24" s="15">
-        <v>2.0443333006297868</v>
+        <v>1.8335833006297864</v>
       </c>
       <c r="L24" s="15">
-        <v>1.971045796517112</v>
+        <v>1.7602957965171115</v>
       </c>
       <c r="M24" s="15">
-        <v>1.9348115019468295</v>
+        <v>1.7240615019468291</v>
       </c>
       <c r="N24" s="15">
-        <v>1.8996046717559407</v>
+        <v>1.6888546717559403</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -29531,22 +29981,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -30373,40 +30823,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.6602038843222422</v>
+        <v>2.4494538843222418</v>
       </c>
       <c r="C48" s="25">
-        <v>2.6595956088586235</v>
+        <v>2.448845608858623</v>
       </c>
       <c r="D48" s="25">
-        <v>2.6600130651854359</v>
+        <v>2.4492630651854355</v>
       </c>
       <c r="E48" s="25">
-        <v>2.667583361947095</v>
+        <v>2.4568333619470946</v>
       </c>
       <c r="F48" s="25">
-        <v>2.6676527307427804</v>
+        <v>2.45690273074278</v>
       </c>
       <c r="G48" s="25">
-        <v>2.6508101928206882</v>
+        <v>2.4400601928206878</v>
       </c>
       <c r="I48" s="28">
-        <v>2.6602038843222422</v>
+        <v>2.4494538843222418</v>
       </c>
       <c r="J48" s="15">
-        <v>2.4505325812502576</v>
+        <v>2.2397825812502572</v>
       </c>
       <c r="K48" s="15">
-        <v>2.3523301962238738</v>
+        <v>2.1415801962238734</v>
       </c>
       <c r="L48" s="15">
-        <v>2.2639349230168682</v>
+        <v>2.0531849230168677</v>
       </c>
       <c r="M48" s="15">
-        <v>2.1849655743701497</v>
+        <v>1.9742155743701493</v>
       </c>
       <c r="N48" s="15">
-        <v>2.100285669463549</v>
+        <v>1.8895356694635486</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -30449,6 +30899,51 @@
       <c r="N49" s="26">
         <v>97.000000441200967</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -30469,7 +30964,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -30496,22 +30991,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -31423,40 +31918,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.2864873855639134</v>
+        <v>2.075737385563913</v>
       </c>
       <c r="C24" s="25">
-        <v>2.2864872191520704</v>
+        <v>2.07573721915207</v>
       </c>
       <c r="D24" s="25">
-        <v>2.2864872063952753</v>
+        <v>2.0757372063952748</v>
       </c>
       <c r="E24" s="25">
-        <v>2.2864872216769578</v>
+        <v>2.0757372216769574</v>
       </c>
       <c r="F24" s="25">
-        <v>2.2864872203432722</v>
+        <v>2.0757372203432718</v>
       </c>
       <c r="G24" s="25">
-        <v>2.2864872215218117</v>
+        <v>2.0757372215218113</v>
       </c>
       <c r="I24" s="28">
-        <v>2.2864872216774725</v>
+        <v>2.0757372216774721</v>
       </c>
       <c r="J24" s="15">
-        <v>2.027850249252245</v>
+        <v>1.8171002492522446</v>
       </c>
       <c r="K24" s="15">
-        <v>1.8839969581033174</v>
+        <v>1.6732469581033169</v>
       </c>
       <c r="L24" s="15">
-        <v>1.7371068229054949</v>
+        <v>1.5263568229054945</v>
       </c>
       <c r="M24" s="15">
-        <v>1.5861211787762139</v>
+        <v>1.3753711787762135</v>
       </c>
       <c r="N24" s="15">
-        <v>1.4679622574256566</v>
+        <v>1.2572122574256561</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -31516,22 +32011,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -32406,40 +32901,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.5363822580466837</v>
+        <v>2.3256322580466833</v>
       </c>
       <c r="C48" s="25">
-        <v>2.5363819763808486</v>
+        <v>2.3256319763808482</v>
       </c>
       <c r="D48" s="25">
-        <v>2.5363819764456137</v>
+        <v>2.3256319764456133</v>
       </c>
       <c r="E48" s="25">
-        <v>2.5363819774533352</v>
+        <v>2.3256319774533347</v>
       </c>
       <c r="F48" s="25">
-        <v>2.5363819767157478</v>
+        <v>2.3256319767157474</v>
       </c>
       <c r="G48" s="25">
-        <v>2.5363819765882698</v>
+        <v>2.3256319765882694</v>
       </c>
       <c r="I48" s="28">
-        <v>2.5363824280950227</v>
+        <v>2.3256324280950222</v>
       </c>
       <c r="J48" s="15">
-        <v>2.2333471799423896</v>
+        <v>2.0225971799423892</v>
       </c>
       <c r="K48" s="15">
-        <v>2.0991258652930989</v>
+        <v>1.8883758652930984</v>
       </c>
       <c r="L48" s="15">
-        <v>1.9570234527806878</v>
+        <v>1.7462734527806874</v>
       </c>
       <c r="M48" s="15">
-        <v>1.8073939214898946</v>
+        <v>1.5966439214898942</v>
       </c>
       <c r="N48" s="15">
-        <v>1.6586392312673188</v>
+        <v>1.4478892312673184</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -32482,6 +32977,51 @@
       <c r="N49" s="26">
         <v>94.999999273793492</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -32502,7 +33042,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="26" style="8" bestFit="1" customWidth="1"/>
@@ -32529,22 +33069,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -33456,40 +33996,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.3572198658819885</v>
+        <v>2.1464698658819881</v>
       </c>
       <c r="C24" s="15">
-        <v>2.3572198657095682</v>
+        <v>2.1464698657095678</v>
       </c>
       <c r="D24" s="15">
-        <v>2.3572198470913586</v>
+        <v>2.1464698470913581</v>
       </c>
       <c r="E24" s="15">
-        <v>2.3572198573413319</v>
+        <v>2.1464698573413314</v>
       </c>
       <c r="F24" s="15">
-        <v>2.3572198522183809</v>
+        <v>2.1464698522183805</v>
       </c>
       <c r="G24" s="15">
-        <v>2.3572198660370001</v>
+        <v>2.1464698660369996</v>
       </c>
       <c r="I24" s="28">
-        <v>2.3572198658819885</v>
+        <v>2.1464698658819881</v>
       </c>
       <c r="J24" s="28">
-        <v>2.0595969144004136</v>
+        <v>1.8488469144004132</v>
       </c>
       <c r="K24" s="28">
-        <v>1.894419677983467</v>
+        <v>1.6836696779834666</v>
       </c>
       <c r="L24" s="28">
-        <v>1.7999858175970609</v>
+        <v>1.5892358175970605</v>
       </c>
       <c r="M24" s="28">
-        <v>1.5485656297182437</v>
+        <v>1.3378156297182433</v>
       </c>
       <c r="N24" s="28">
-        <v>1.5385204758209776</v>
+        <v>1.3277704758209772</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -33549,22 +34089,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -34439,40 +34979,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.664779644614574</v>
+        <v>2.4540296446145735</v>
       </c>
       <c r="C48" s="25">
-        <v>2.6647796575358811</v>
+        <v>2.4540296575358806</v>
       </c>
       <c r="D48" s="25">
-        <v>2.6647796574368079</v>
+        <v>2.4540296574368075</v>
       </c>
       <c r="E48" s="25">
-        <v>2.6647796573243689</v>
+        <v>2.4540296573243685</v>
       </c>
       <c r="F48" s="25">
-        <v>2.6647814430025547</v>
+        <v>2.4540314430025543</v>
       </c>
       <c r="G48" s="25">
-        <v>2.6647812694646671</v>
+        <v>2.4540312694646667</v>
       </c>
       <c r="I48" s="28">
-        <v>2.6647796575509011</v>
+        <v>2.4540296575509006</v>
       </c>
       <c r="J48" s="15">
-        <v>2.3950511659685283</v>
+        <v>2.1843011659685279</v>
       </c>
       <c r="K48" s="15">
-        <v>2.2456908954580155</v>
+        <v>2.034940895458015</v>
       </c>
       <c r="L48" s="15">
-        <v>2.0879546637338935</v>
+        <v>1.8772046637338931</v>
       </c>
       <c r="M48" s="15">
-        <v>1.9222566712951901</v>
+        <v>1.7115066712951896</v>
       </c>
       <c r="N48" s="15">
-        <v>1.7486453561575901</v>
+        <v>1.5378953561575897</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -34515,6 +35055,51 @@
       <c r="N49" s="26">
         <v>95.999999704946333</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -34535,7 +35120,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W97"/>
+  <dimension ref="A1:W103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -34562,22 +35147,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -35465,40 +36050,40 @@
         <v>78</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1355543109495292</v>
+        <v>1.9248043109495288</v>
       </c>
       <c r="C24" s="25">
-        <v>2.2967316022458864</v>
+        <v>2.0859816022458859</v>
       </c>
       <c r="D24" s="25">
-        <v>2.2967316022455995</v>
+        <v>2.085981602245599</v>
       </c>
       <c r="E24" s="25">
-        <v>2.2967316022424926</v>
+        <v>2.0859816022424922</v>
       </c>
       <c r="F24" s="25">
-        <v>2.2967316022420228</v>
+        <v>2.0859816022420223</v>
       </c>
       <c r="G24" s="25">
-        <v>2.29673160223961</v>
+        <v>2.0859816022396096</v>
       </c>
       <c r="I24" s="28">
-        <v>2.1358738891520925</v>
+        <v>1.9251238891520921</v>
       </c>
       <c r="J24" s="15">
-        <v>2.0703785633032981</v>
+        <v>1.8596285633032976</v>
       </c>
       <c r="K24" s="15">
-        <v>2.0596609830905779</v>
+        <v>1.8489109830905774</v>
       </c>
       <c r="L24" s="15">
-        <v>2.0372071959396196</v>
+        <v>1.8264571959396192</v>
       </c>
       <c r="M24" s="15">
-        <v>2.0079788255291753</v>
+        <v>1.7972288255291748</v>
       </c>
       <c r="N24" s="15">
-        <v>1.9833265400814226</v>
+        <v>1.7725765400814222</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -35558,22 +36143,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -36424,40 +37009,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.2022685430187843</v>
+        <v>1.9915185430187838</v>
       </c>
       <c r="C48" s="25">
-        <v>2.2022686000014877</v>
+        <v>1.9915186000014873</v>
       </c>
       <c r="D48" s="25">
-        <v>2.2022685997284071</v>
+        <v>1.9915185997284066</v>
       </c>
       <c r="E48" s="25">
-        <v>2.2022686001008398</v>
+        <v>1.9915186001008394</v>
       </c>
       <c r="F48" s="25">
-        <v>2.202268596720963</v>
+        <v>1.9915185967209625</v>
       </c>
       <c r="G48" s="25">
-        <v>2.2022686000728946</v>
+        <v>1.9915186000728942</v>
       </c>
       <c r="I48" s="28">
-        <v>2.2022686000754255</v>
+        <v>1.991518600075425</v>
       </c>
       <c r="J48" s="15">
-        <v>2.1070219395840275</v>
+        <v>1.8962719395840271</v>
       </c>
       <c r="K48" s="15">
-        <v>2.0593986605953591</v>
+        <v>1.8486486605953587</v>
       </c>
       <c r="L48" s="15">
-        <v>2.0318362925785767</v>
+        <v>1.8210862925785762</v>
       </c>
       <c r="M48" s="15">
-        <v>2.0079804670903565</v>
+        <v>1.7972304670903561</v>
       </c>
       <c r="N48" s="15">
-        <v>1.983328159147024</v>
+        <v>1.7725781591470235</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.15">
@@ -36503,22 +37088,22 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A52" s="12"/>
-      <c r="B52" s="38" t="s">
+      <c r="B52" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="I52" s="38" t="s">
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37"/>
+      <c r="I52" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J52" s="38"/>
-      <c r="K52" s="38"/>
-      <c r="L52" s="38"/>
-      <c r="M52" s="38"/>
-      <c r="N52" s="38"/>
+      <c r="J52" s="37"/>
+      <c r="K52" s="37"/>
+      <c r="L52" s="37"/>
+      <c r="M52" s="37"/>
+      <c r="N52" s="37"/>
     </row>
     <row r="53" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A53" s="13" t="s">
@@ -37406,40 +37991,40 @@
         <v>47</v>
       </c>
       <c r="B72" s="15">
-        <v>2.3269191722498097</v>
+        <v>2.1161691722498093</v>
       </c>
       <c r="C72" s="25">
-        <v>2.3338237319856656</v>
+        <v>2.1230737319856652</v>
       </c>
       <c r="D72" s="25">
-        <v>2.3338237319861292</v>
+        <v>2.1230737319861288</v>
       </c>
       <c r="E72" s="25">
-        <v>2.3338237319854338</v>
+        <v>2.1230737319854334</v>
       </c>
       <c r="F72" s="25">
-        <v>2.3338237319860102</v>
+        <v>2.1230737319860098</v>
       </c>
       <c r="G72" s="25">
-        <v>2.3338237319853752</v>
+        <v>2.1230737319853747</v>
       </c>
       <c r="I72" s="28">
-        <v>2.3338237319854174</v>
+        <v>2.1230737319854169</v>
       </c>
       <c r="J72" s="15">
-        <v>2.168762844812151</v>
+        <v>1.9580128448121505</v>
       </c>
       <c r="K72" s="15">
-        <v>2.1121018851729829</v>
+        <v>1.9013518851729825</v>
       </c>
       <c r="L72" s="15">
-        <v>2.06383423710475</v>
+        <v>1.8530842371047496</v>
       </c>
       <c r="M72" s="15">
-        <v>2.0155666502547369</v>
+        <v>1.8048166502547365</v>
       </c>
       <c r="N72" s="15">
-        <v>1.9748019199124032</v>
+        <v>1.7640519199124027</v>
       </c>
       <c r="Q72" s="29"/>
       <c r="R72" s="18"/>
@@ -37499,22 +38084,22 @@
     </row>
     <row r="76" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="12"/>
-      <c r="B76" s="38" t="s">
+      <c r="B76" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C76" s="38"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="38"/>
-      <c r="I76" s="38" t="s">
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37"/>
+      <c r="I76" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J76" s="38"/>
-      <c r="K76" s="38"/>
-      <c r="L76" s="38"/>
-      <c r="M76" s="38"/>
-      <c r="N76" s="38"/>
+      <c r="J76" s="37"/>
+      <c r="K76" s="37"/>
+      <c r="L76" s="37"/>
+      <c r="M76" s="37"/>
+      <c r="N76" s="37"/>
     </row>
     <row r="77" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A77" s="13" t="s">
@@ -38365,40 +38950,40 @@
         <v>47</v>
       </c>
       <c r="B96" s="15">
-        <v>2.4980147168460656</v>
+        <v>2.2872647168460651</v>
       </c>
       <c r="C96" s="25">
-        <v>2.4980170143730316</v>
+        <v>2.2872670143730311</v>
       </c>
       <c r="D96" s="25">
-        <v>2.4980147168443088</v>
+        <v>2.2872647168443083</v>
       </c>
       <c r="E96" s="25">
-        <v>2.4980147168442466</v>
+        <v>2.2872647168442461</v>
       </c>
       <c r="F96" s="25">
-        <v>2.4853191739834375</v>
+        <v>2.2745691739834371</v>
       </c>
       <c r="G96" s="25">
-        <v>2.4572459329261713</v>
+        <v>2.2464959329261709</v>
       </c>
       <c r="I96" s="28">
-        <v>2.4980147168443088</v>
+        <v>2.2872647168443083</v>
       </c>
       <c r="J96" s="15">
-        <v>2.2975287233014541</v>
+        <v>2.0867787233014536</v>
       </c>
       <c r="K96" s="15">
-        <v>2.2037314124448808</v>
+        <v>1.9929814124448804</v>
       </c>
       <c r="L96" s="15">
-        <v>2.1140331457031154</v>
+        <v>1.903283145703115</v>
       </c>
       <c r="M96" s="15">
-        <v>2.0642234256543071</v>
+        <v>1.8534734256543066</v>
       </c>
       <c r="N96" s="15">
-        <v>2.0166001441918051</v>
+        <v>1.8058501441918047</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.15">
@@ -38441,6 +39026,81 @@
       <c r="N97" s="26">
         <v>95.000000795117828</v>
       </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="M99" s="8"/>
+      <c r="N99" s="8"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
+      <c r="N100" s="8"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+      <c r="M101" s="8"/>
+      <c r="N101" s="8"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+      <c r="M102" s="8"/>
+      <c r="N102" s="8"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="8"/>
+      <c r="J103" s="8"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+      <c r="M103" s="8"/>
+      <c r="N103" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -38465,7 +39125,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -38492,22 +39152,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="I4" s="38" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -39419,40 +40079,40 @@
         <v>47</v>
       </c>
       <c r="B24" s="15">
-        <v>2.3364873855639132</v>
+        <v>2.1257373855639128</v>
       </c>
       <c r="C24" s="25">
-        <v>2.3364872191520702</v>
+        <v>2.1257372191520698</v>
       </c>
       <c r="D24" s="25">
-        <v>2.3364872063952751</v>
+        <v>2.1257372063952746</v>
       </c>
       <c r="E24" s="25">
-        <v>2.3364872216769577</v>
+        <v>2.1257372216769572</v>
       </c>
       <c r="F24" s="25">
-        <v>2.3364872203432721</v>
+        <v>2.1257372203432716</v>
       </c>
       <c r="G24" s="25">
-        <v>2.3364872215218115</v>
+        <v>2.1257372215218111</v>
       </c>
       <c r="I24" s="28">
-        <v>2.3364872216774724</v>
+        <v>2.1257372216774719</v>
       </c>
       <c r="J24" s="15">
-        <v>2.0778502492522453</v>
+        <v>1.8671002492522448</v>
       </c>
       <c r="K24" s="15">
-        <v>1.9339969581033174</v>
+        <v>1.723246958103317</v>
       </c>
       <c r="L24" s="15">
-        <v>1.7871068229054949</v>
+        <v>1.5763568229054945</v>
       </c>
       <c r="M24" s="15">
-        <v>1.636121178776214</v>
+        <v>1.4253711787762136</v>
       </c>
       <c r="N24" s="15">
-        <v>1.5179622574256566</v>
+        <v>1.3072122574256562</v>
       </c>
       <c r="Q24" s="29"/>
       <c r="R24" s="18"/>
@@ -39512,22 +40172,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="I28" s="38" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -40402,40 +41062,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="15">
-        <v>2.5863822580466835</v>
+        <v>2.3756322580466831</v>
       </c>
       <c r="C48" s="25">
-        <v>2.5863819763808484</v>
+        <v>2.375631976380848</v>
       </c>
       <c r="D48" s="25">
-        <v>2.5863819764456135</v>
+        <v>2.3756319764456131</v>
       </c>
       <c r="E48" s="25">
-        <v>2.586381977453335</v>
+        <v>2.3756319774533345</v>
       </c>
       <c r="F48" s="25">
-        <v>2.5863819767157477</v>
+        <v>2.3756319767157472</v>
       </c>
       <c r="G48" s="25">
-        <v>2.5863819765882696</v>
+        <v>2.3756319765882692</v>
       </c>
       <c r="I48" s="28">
-        <v>2.5863824280950225</v>
+        <v>2.3756324280950221</v>
       </c>
       <c r="J48" s="15">
-        <v>2.2833471799423894</v>
+        <v>2.072597179942389</v>
       </c>
       <c r="K48" s="15">
-        <v>2.1491258652930987</v>
+        <v>1.9383758652930982</v>
       </c>
       <c r="L48" s="15">
-        <v>2.0070234527806878</v>
+        <v>1.7962734527806874</v>
       </c>
       <c r="M48" s="15">
-        <v>1.8573939214898947</v>
+        <v>1.6466439214898942</v>
       </c>
       <c r="N48" s="15">
-        <v>1.7086392312673189</v>
+        <v>1.4978892312673184</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -40478,6 +41138,51 @@
       <c r="N49" s="26">
         <v>94.999999273793492</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
